--- a/public/templates/000_pm_suite/02_프로젝트 개발/06_검수/01_단위테스트/프로젝트명_단위테스트시나리오_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/06_검수/01_단위테스트/프로젝트명_단위테스트시나리오_V1.0_20230530.xlsx
@@ -9,10 +9,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서이력" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="현황" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01.시안처리및OCR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01.도서파싱및OCR" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02.3단계AI판정" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03.문안대조및대체" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04.RA전문심의" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03.조항대조및치환" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04.QA법무전문검토" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05.시스템및연계" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
@@ -3075,12 +3075,12 @@
     <row r="12" ht="21" customHeight="1" s="185">
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI</t>
+          <t>한빛글로벌 SyncFlow AI</t>
         </is>
       </c>
       <c r="C12" s="139" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="186" t="n"/>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -3433,7 +3433,7 @@
     <row r="1" ht="26.25" customHeight="1" s="185">
       <c r="A1" s="147" t="inlineStr">
         <is>
-          <t>SyncGuard AI 단위테스트 결과 및 조치 현황</t>
+          <t>SyncFlow AI 단위테스트 결과 및 조치 현황</t>
         </is>
       </c>
       <c r="J1" s="6" t="n"/>
@@ -3623,11 +3623,11 @@
     <row r="5" ht="37.5" customHeight="1" s="185">
       <c r="A5" s="131" t="inlineStr">
         <is>
-          <t>01.시안처리및OCR</t>
+          <t>01.도서파싱및OCR</t>
         </is>
       </c>
       <c r="B5" s="202">
-        <f>COUNTA('01.시안처리및OCR'!$A$5:$A$100)</f>
+        <f>COUNTA('01.도서파싱및OCR'!$A$5:$A$100)</f>
         <v/>
       </c>
       <c r="C5" s="202" t="n"/>
@@ -3638,11 +3638,11 @@
         <v/>
       </c>
       <c r="G5" s="204">
-        <f>COUNTA('01.시안처리및OCR'!$C$5:$C$100)</f>
+        <f>COUNTA('01.도서파싱및OCR'!$C$5:$C$100)</f>
         <v/>
       </c>
       <c r="H5" s="205">
-        <f>COUNTIF('01.시안처리및OCR'!$K$5:$K$100,H$4)</f>
+        <f>COUNTIF('01.도서파싱및OCR'!$K$5:$K$100,H$4)</f>
         <v/>
       </c>
       <c r="I5" s="206">
@@ -3654,7 +3654,7 @@
         <v/>
       </c>
       <c r="K5" s="208">
-        <f>COUNTIF('01.시안처리및OCR'!$K$5:$K$100,K$4)</f>
+        <f>COUNTIF('01.도서파싱및OCR'!$K$5:$K$100,K$4)</f>
         <v/>
       </c>
       <c r="L5" s="209">
@@ -3787,11 +3787,11 @@
     <row r="7" ht="37.5" customHeight="1" s="185">
       <c r="A7" s="132" t="inlineStr">
         <is>
-          <t>03.문안대조및대체</t>
+          <t>03.조항대조및치환</t>
         </is>
       </c>
       <c r="B7" s="202">
-        <f>COUNTA('03.문안대조및대체'!$A$5:$A$100)</f>
+        <f>COUNTA('03.조항대조및치환'!$A$5:$A$100)</f>
         <v/>
       </c>
       <c r="C7" s="202" t="n"/>
@@ -3802,11 +3802,11 @@
         <v/>
       </c>
       <c r="G7" s="204">
-        <f>COUNTA('03.문안대조및대체'!$C$5:$C$100)</f>
+        <f>COUNTA('03.조항대조및치환'!$C$5:$C$100)</f>
         <v/>
       </c>
       <c r="H7" s="205">
-        <f>COUNTIF('03.문안대조및대체'!$K$5:$K$100,H$4)</f>
+        <f>COUNTIF('03.조항대조및치환'!$K$5:$K$100,H$4)</f>
         <v/>
       </c>
       <c r="I7" s="206">
@@ -3818,7 +3818,7 @@
         <v/>
       </c>
       <c r="K7" s="208">
-        <f>COUNTIF('03.문안대조및대체'!$K$5:$K$100,K$4)</f>
+        <f>COUNTIF('03.조항대조및치환'!$K$5:$K$100,K$4)</f>
         <v/>
       </c>
       <c r="L7" s="209">
@@ -3869,11 +3869,11 @@
     <row r="8" ht="37.5" customHeight="1" s="185">
       <c r="A8" s="132" t="inlineStr">
         <is>
-          <t>04.RA전문심의</t>
+          <t>04.QA법무전문검토</t>
         </is>
       </c>
       <c r="B8" s="202">
-        <f>COUNTA('04.RA전문심의'!$A$5:$A$100)</f>
+        <f>COUNTA('04.QA법무전문검토'!$A$5:$A$100)</f>
         <v/>
       </c>
       <c r="C8" s="202" t="n"/>
@@ -3884,11 +3884,11 @@
         <v/>
       </c>
       <c r="G8" s="204">
-        <f>COUNTA('04.RA전문심의'!$C$5:$C$100)</f>
+        <f>COUNTA('04.QA법무전문검토'!$C$5:$C$100)</f>
         <v/>
       </c>
       <c r="H8" s="205">
-        <f>COUNTIF('04.RA전문심의'!$K$5:$K$100,H$4)</f>
+        <f>COUNTIF('04.QA법무전문검토'!$K$5:$K$100,H$4)</f>
         <v/>
       </c>
       <c r="I8" s="206">
@@ -3900,7 +3900,7 @@
         <v/>
       </c>
       <c r="K8" s="208">
-        <f>COUNTIF('04.RA전문심의'!$K$5:$K$100,K$4)</f>
+        <f>COUNTIF('04.QA법무전문검토'!$K$5:$K$100,K$4)</f>
         <v/>
       </c>
       <c r="L8" s="209">
@@ -4289,7 +4289,7 @@
     <row r="1" ht="20.25" customHeight="1" s="185">
       <c r="A1" s="238" t="inlineStr">
         <is>
-          <t>01.시안처리및OCR</t>
+          <t>01.도서파싱및OCR</t>
         </is>
       </c>
       <c r="C1" s="12" t="n"/>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B5" s="248" t="inlineStr">
         <is>
-          <t>PPTX 시안 파싱</t>
+          <t>PPTX 계약·도서 파싱</t>
         </is>
       </c>
       <c r="C5" s="247" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E5" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F5" s="248" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B6" s="248" t="inlineStr">
         <is>
-          <t>PPTX 시안 파싱</t>
+          <t>PPTX 계약·도서 파싱</t>
         </is>
       </c>
       <c r="C6" s="247" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E6" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F6" s="248" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B7" s="248" t="inlineStr">
         <is>
-          <t>PPTX 시안 파싱</t>
+          <t>PPTX 계약·도서 파싱</t>
         </is>
       </c>
       <c r="C7" s="247" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="E7" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F7" s="248" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B8" s="248" t="inlineStr">
         <is>
-          <t>PPTX 시안 파싱</t>
+          <t>PPTX 계약·도서 파싱</t>
         </is>
       </c>
       <c r="C8" s="247" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E8" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F8" s="248" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>한국어 카피 OCR 인식률</t>
+          <t>한국어 조항 OCR 인식률</t>
         </is>
       </c>
       <c r="E9" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F9" s="248" t="inlineStr">
         <is>
-          <t>상세페이지 이미지 내 한글 폰트 인식률 95% 이상 달성</t>
+          <t>기술시방서 이미지 내 한글 폰트 인식률 95% 이상 달성</t>
         </is>
       </c>
       <c r="G9" s="249" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="E10" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F10" s="248" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E11" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F11" s="248" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E12" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F12" s="248" t="inlineStr">
         <is>
-          <t>한영 혼용 화장품 성분명 및 브랜드명 깨짐 없이 인식</t>
+          <t>한영 혼용 전장부품 성분명 및 사업본부명 깨짐 없이 인식</t>
         </is>
       </c>
       <c r="G12" s="249" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="E13" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F13" s="248" t="inlineStr">
         <is>
-          <t>디자인 줄바꿈으로 끊어진 카피 문구를 단일 문장으로 결합</t>
+          <t>디자인 줄바꿈으로 끊어진 조항 조항을 단일 문장으로 결합</t>
         </is>
       </c>
       <c r="G13" s="249" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="E14" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F14" s="248" t="inlineStr">
         <is>
-          <t>심의에 불필요한 특수문자 정제 및 강조 기호 보존</t>
+          <t>검증에 불필요한 특수문자 정제 및 강조 기호 보존</t>
         </is>
       </c>
       <c r="G14" s="249" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E15" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F15" s="248" t="inlineStr">
         <is>
-          <t>상세페이지 상단에서 하단으로 시각적 흐름 순 정렬</t>
+          <t>기술시방서 상단에서 하단으로 시각적 흐름 순 정렬</t>
         </is>
       </c>
       <c r="G15" s="249" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="E16" s="247" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F16" s="248" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>의약품 오인 표현 즉시 매칭</t>
+          <t>불공정 독소조항 표현 즉시 매칭</t>
         </is>
       </c>
       <c r="E5" s="247" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="F5" s="248" t="inlineStr">
         <is>
-          <t>치료, 재생, 완치 등 금지 표현 즉시 BAN 판정</t>
+          <t>면책, 재생, 전가 등 금지 표현 즉시 BAN 판정</t>
         </is>
       </c>
       <c r="G5" s="249" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="F6" s="248" t="inlineStr">
         <is>
-          <t>국내 최초, 100% 무자극 등 절대 표현 WARN 판정</t>
+          <t>국내 최초, 100% 무결함 등 절대 표현 WARN 판정</t>
         </is>
       </c>
       <c r="G6" s="249" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D7" s="248" t="inlineStr">
         <is>
-          <t>화장품 금지 원료 표현 필터링</t>
+          <t>전장부품 금지 원소재 표현 필터링</t>
         </is>
       </c>
       <c r="E7" s="247" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F7" s="248" t="inlineStr">
         <is>
-          <t>화장품 배합 금지 성분 표기 즉시 적발 및 근거 매핑</t>
+          <t>전장부품 조성 금지 성분 표기 즉시 적발 및 근거 매핑</t>
         </is>
       </c>
       <c r="G7" s="249" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="F8" s="248" t="inlineStr">
         <is>
-          <t>재생시켜주는, 치료효과 등 어미 변형 패턴 정규식 매칭</t>
+          <t>재생시켜주는, 면책효과 등 어미 변형 패턴 정규식 매칭</t>
         </is>
       </c>
       <c r="G8" s="249" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>식약처 처분사례 벡터 검색</t>
+          <t>공정위·표준원 심결사례 벡터 검색</t>
         </is>
       </c>
       <c r="E9" s="247" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="F9" s="248" t="inlineStr">
         <is>
-          <t>pgvector 코사인 유사도 0.85 이상 유사 행정처분 3건 검색</t>
+          <t>pgvector 코사인 유사도 0.85 이상 유사 시정명령·심결 3건 검색</t>
         </is>
       </c>
       <c r="G9" s="249" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D10" s="248" t="inlineStr">
         <is>
-          <t>유사 처분 문안 하이라이트</t>
+          <t>유사 처분 계약조항 하이라이트</t>
         </is>
       </c>
       <c r="E10" s="247" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F10" s="248" t="inlineStr">
         <is>
-          <t>매칭된 과거 처분 문안과 현재 심의 문안의 유사 단어 강조</t>
+          <t>매칭된 과거 처분 계약조항과 현재 검증 계약조항의 유사 단어 강조</t>
         </is>
       </c>
       <c r="G10" s="249" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B12" s="248" t="inlineStr">
         <is>
-          <t>3단계 Agent 문맥심의</t>
+          <t>3단계 Agent 문맥검증</t>
         </is>
       </c>
       <c r="C12" s="247" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B13" s="248" t="inlineStr">
         <is>
-          <t>3단계 Agent 문맥심의</t>
+          <t>3단계 Agent 문맥검증</t>
         </is>
       </c>
       <c r="C13" s="247" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D13" s="248" t="inlineStr">
         <is>
-          <t>인체적용시험 시험 조건 대조</t>
+          <t>공인신뢰성시험 시험 조건 대조</t>
         </is>
       </c>
       <c r="E13" s="247" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="F13" s="248" t="inlineStr">
         <is>
-          <t>실증 시험 대상, 기간 표기 누락 시 실증 요구 태그 판정</t>
+          <t>시험검증 시험 대상, 기간 표기 누락 시 시험검증 요구 태그 판정</t>
         </is>
       </c>
       <c r="G13" s="249" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="B14" s="248" t="inlineStr">
         <is>
-          <t>3단계 Agent 문맥심의</t>
+          <t>3단계 Agent 문맥검증</t>
         </is>
       </c>
       <c r="C14" s="247" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="B15" s="248" t="inlineStr">
         <is>
-          <t>3단계 Agent 문맥심의</t>
+          <t>3단계 Agent 문맥검증</t>
         </is>
       </c>
       <c r="C15" s="247" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="B16" s="248" t="inlineStr">
         <is>
-          <t>3단계 Agent 문맥심의</t>
+          <t>3단계 Agent 문맥검증</t>
         </is>
       </c>
       <c r="C16" s="247" t="inlineStr">
@@ -9597,7 +9597,7 @@
     <row r="1" ht="20.25" customHeight="1" s="185">
       <c r="A1" s="238" t="inlineStr">
         <is>
-          <t>03.문안대조및대체</t>
+          <t>03.조항대조및치환</t>
         </is>
       </c>
       <c r="C1" s="12" t="n"/>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>원본 시안 ↔ 추출 문장 동기화</t>
+          <t>원본 계약·도서 ↔ 추출 문장 동기화</t>
         </is>
       </c>
       <c r="E5" s="247" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="F5" s="248" t="inlineStr">
         <is>
-          <t>좌측 시안 영역과 우측 문장 카드가 1:1 수평 대응 렌더링</t>
+          <t>좌측 계약·도서 영역과 우측 문장 카드가 1:1 수평 대응 렌더링</t>
         </is>
       </c>
       <c r="G5" s="249" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="F7" s="248" t="inlineStr">
         <is>
-          <t>우측 문장 클릭 시 좌측 시안 내 해당 영역으로 부드럽게 스크롤</t>
+          <t>우측 문장 클릭 시 좌측 계약·도서 내 해당 영역으로 부드럽게 스크롤</t>
         </is>
       </c>
       <c r="G7" s="249" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="D8" s="248" t="inlineStr">
         <is>
-          <t>시안 확대/축소 및 패닝 조작</t>
+          <t>계약·도서 확대/축소 및 패닝 조작</t>
         </is>
       </c>
       <c r="E8" s="247" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>안전 대체 문안 3종 제시</t>
+          <t>안전 대체 계약조항 3종 제시</t>
         </is>
       </c>
       <c r="E9" s="247" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="F9" s="248" t="inlineStr">
         <is>
-          <t>식약처 심의 승인 완료된 안전 대체 카피 3건 추천</t>
+          <t>공정위·표준원 검증 승인 완료된 안전 대체 조항 3건 추천</t>
         </is>
       </c>
       <c r="G9" s="249" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="D10" s="248" t="inlineStr">
         <is>
-          <t>대체어 원클릭 치환 반영</t>
+          <t>표준대안 원클릭 치환 반영</t>
         </is>
       </c>
       <c r="E10" s="247" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="F10" s="248" t="inlineStr">
         <is>
-          <t>추천 문안 클릭 시 본문 즉시 변경 및 AI 실시간 재판정</t>
+          <t>추천 계약조항 클릭 시 본문 즉시 변경 및 AI 실시간 재판정</t>
         </is>
       </c>
       <c r="G10" s="249" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="D11" s="248" t="inlineStr">
         <is>
-          <t>사용자 수동 문안 직접 수정</t>
+          <t>사용자 수동 계약조항 직접 수정</t>
         </is>
       </c>
       <c r="E11" s="247" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="F11" s="248" t="inlineStr">
         <is>
-          <t>마케터가 텍스트 직접 타이핑 수정 후 재심의 호출</t>
+          <t>구매담당자가 텍스트 직접 타이핑 수정 후 재검증 호출</t>
         </is>
       </c>
       <c r="G11" s="249" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B12" s="248" t="inlineStr">
         <is>
-          <t>실증 자료 및 소명</t>
+          <t>시험성적서 및 소명</t>
         </is>
       </c>
       <c r="C12" s="247" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="D12" s="248" t="inlineStr">
         <is>
-          <t>ProductLab 실증문서 연계 뷰어</t>
+          <t>PLM-Nexus 시험검증문서 연계 뷰어</t>
         </is>
       </c>
       <c r="E12" s="247" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="F12" s="248" t="inlineStr">
         <is>
-          <t>연결된 인체적용시험 성적서 요약 모달 팝업 표시</t>
+          <t>연결된 공인신뢰성시험 성적서 요약 모달 팝업 표시</t>
         </is>
       </c>
       <c r="G12" s="249" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="B13" s="248" t="inlineStr">
         <is>
-          <t>실증 자료 및 소명</t>
+          <t>시험성적서 및 소명</t>
         </is>
       </c>
       <c r="C13" s="247" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="F13" s="248" t="inlineStr">
         <is>
-          <t>마케터가 신규 시험성적서(PDF) 업로드 및 소명 사유 입력</t>
+          <t>구매담당자가 신규 시험성적서(PDF) 업로드 및 소명 사유 입력</t>
         </is>
       </c>
       <c r="G13" s="249" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="B14" s="248" t="inlineStr">
         <is>
-          <t>실증 자료 및 소명</t>
+          <t>시험성적서 및 소명</t>
         </is>
       </c>
       <c r="C14" s="247" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="D14" s="248" t="inlineStr">
         <is>
-          <t>심의 의뢰 제출 및 유효성 체크</t>
+          <t>검증 요청 제출 및 유효성 체크</t>
         </is>
       </c>
       <c r="E14" s="247" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="F14" s="248" t="inlineStr">
         <is>
-          <t>필수 입력값 누락 시 안내 및 완료 시 RA 접수 큐 전송</t>
+          <t>필수 입력값 누락 시 안내 및 완료 시 QA 접수 큐 전송</t>
         </is>
       </c>
       <c r="G14" s="249" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="B15" s="248" t="inlineStr">
         <is>
-          <t>실증 자료 및 소명</t>
+          <t>시험성적서 및 소명</t>
         </is>
       </c>
       <c r="C15" s="247" t="inlineStr">
@@ -12121,7 +12121,7 @@
     <row r="1" ht="20.25" customHeight="1" s="185">
       <c r="A1" s="238" t="inlineStr">
         <is>
-          <t>04.RA전문심의</t>
+          <t>04.QA법무전문검토</t>
         </is>
       </c>
       <c r="C1" s="12" t="n"/>
@@ -12238,32 +12238,32 @@
     <row r="5">
       <c r="A5" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0100</t>
+          <t>TS_QA_0100</t>
         </is>
       </c>
       <c r="B5" s="248" t="inlineStr">
         <is>
-          <t>심의 접수 관리</t>
+          <t>검증 접수 관리</t>
         </is>
       </c>
       <c r="C5" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0101</t>
+          <t>TC_QA_0101</t>
         </is>
       </c>
       <c r="D5" s="248" t="inlineStr">
         <is>
-          <t>심의 대기 그리드 목록 조회</t>
+          <t>검토 대기 그리드 목록 조회</t>
         </is>
       </c>
       <c r="E5" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="F5" s="248" t="inlineStr">
         <is>
-          <t>브랜드, 의뢰일시, 위험도순 정렬 및 다중 필터링</t>
+          <t>사업본부, 의뢰일시, 위험도순 정렬 및 다중 필터링</t>
         </is>
       </c>
       <c r="G5" s="249" t="inlineStr">
@@ -12303,32 +12303,32 @@
     <row r="6">
       <c r="A6" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0100</t>
+          <t>TS_QA_0100</t>
         </is>
       </c>
       <c r="B6" s="248" t="inlineStr">
         <is>
-          <t>심의 접수 관리</t>
+          <t>검증 접수 관리</t>
         </is>
       </c>
       <c r="C6" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0102</t>
+          <t>TC_QA_0102</t>
         </is>
       </c>
       <c r="D6" s="248" t="inlineStr">
         <is>
-          <t>긴급 심의 플래그 처리</t>
+          <t>긴급 검증 플래그 처리</t>
         </is>
       </c>
       <c r="E6" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="F6" s="248" t="inlineStr">
         <is>
-          <t>마케터 긴급 의뢰 건에 대해 최상단 고정 및 빨간색 알림 표시</t>
+          <t>구매담당자 긴급 의뢰 건에 대해 최상단 고정 및 빨간색 알림 표시</t>
         </is>
       </c>
       <c r="G6" s="249" t="inlineStr">
@@ -12368,17 +12368,17 @@
     <row r="7">
       <c r="A7" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0200</t>
+          <t>TS_QA_0200</t>
         </is>
       </c>
       <c r="B7" s="248" t="inlineStr">
         <is>
-          <t>전문 심의 콘솔</t>
+          <t>전문 검증 콘솔</t>
         </is>
       </c>
       <c r="C7" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0201</t>
+          <t>TC_QA_0201</t>
         </is>
       </c>
       <c r="D7" s="248" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="E7" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F7" s="248" t="inlineStr">
@@ -12433,17 +12433,17 @@
     <row r="8">
       <c r="A8" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0200</t>
+          <t>TS_QA_0200</t>
         </is>
       </c>
       <c r="B8" s="248" t="inlineStr">
         <is>
-          <t>전문 심의 콘솔</t>
+          <t>전문 검증 콘솔</t>
         </is>
       </c>
       <c r="C8" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0202</t>
+          <t>TC_QA_0202</t>
         </is>
       </c>
       <c r="D8" s="248" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="E8" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F8" s="248" t="inlineStr">
@@ -12498,32 +12498,32 @@
     <row r="9">
       <c r="A9" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0200</t>
+          <t>TS_QA_0200</t>
         </is>
       </c>
       <c r="B9" s="248" t="inlineStr">
         <is>
-          <t>전문 심의 콘솔</t>
+          <t>전문 검증 콘솔</t>
         </is>
       </c>
       <c r="C9" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0203</t>
+          <t>TC_QA_0203</t>
         </is>
       </c>
       <c r="D9" s="248" t="inlineStr">
         <is>
-          <t>수정 권고 문구 작성 및 반려</t>
+          <t>수정 권고 조항 작성 및 반려</t>
         </is>
       </c>
       <c r="E9" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F9" s="248" t="inlineStr">
         <is>
-          <t>불가 문안에 대해 마케터 수정 가이드라인 작성 후 반려 전송</t>
+          <t>불가 계약조항에 대해 구매담당자 수정 가이드라인 작성 후 반려 전송</t>
         </is>
       </c>
       <c r="G9" s="249" t="inlineStr">
@@ -12563,32 +12563,32 @@
     <row r="10">
       <c r="A10" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0200</t>
+          <t>TS_QA_0200</t>
         </is>
       </c>
       <c r="B10" s="248" t="inlineStr">
         <is>
-          <t>전문 심의 콘솔</t>
+          <t>전문 검증 콘솔</t>
         </is>
       </c>
       <c r="C10" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0204</t>
+          <t>TC_QA_0204</t>
         </is>
       </c>
       <c r="D10" s="248" t="inlineStr">
         <is>
-          <t>최종 심의 확정 승인 처리</t>
+          <t>최종 검증 확정 승인 처리</t>
         </is>
       </c>
       <c r="E10" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F10" s="248" t="inlineStr">
         <is>
-          <t>전자 서명 검증 및 심의 상태 APPROVED 최종 락 처리</t>
+          <t>전자 서명 검증 및 검증 상태 APPROVED 최종 락 처리</t>
         </is>
       </c>
       <c r="G10" s="249" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="11">
       <c r="A11" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0300</t>
+          <t>TS_QA_0300</t>
         </is>
       </c>
       <c r="B11" s="248" t="inlineStr">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C11" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0301</t>
+          <t>TC_QA_0301</t>
         </is>
       </c>
       <c r="D11" s="248" t="inlineStr">
         <is>
-          <t>심의 결과 공문 PDF 자동 생성</t>
+          <t>검증 결과 공문 PDF 자동 생성</t>
         </is>
       </c>
       <c r="E11" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F11" s="248" t="inlineStr">
         <is>
-          <t>A4 공문 양식 표지, 상세 대조표, RA 서명 포함 PDF 생성</t>
+          <t>A4 공문 양식 표지, 상세 대조표, QA 서명 포함 PDF 생성</t>
         </is>
       </c>
       <c r="G11" s="249" t="inlineStr">
@@ -12693,7 +12693,7 @@
     <row r="12">
       <c r="A12" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0300</t>
+          <t>TS_QA_0300</t>
         </is>
       </c>
       <c r="B12" s="248" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="C12" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0302</t>
+          <t>TC_QA_0302</t>
         </is>
       </c>
       <c r="D12" s="248" t="inlineStr">
@@ -12713,7 +12713,7 @@
       </c>
       <c r="E12" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F12" s="248" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="13">
       <c r="A13" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0300</t>
+          <t>TS_QA_0300</t>
         </is>
       </c>
       <c r="B13" s="248" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="C13" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0303</t>
+          <t>TC_QA_0303</t>
         </is>
       </c>
       <c r="D13" s="248" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E13" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F13" s="248" t="inlineStr">
         <is>
-          <t>시안 v1.0, v1.1, 최종 확정본 간의 문구 차이점 비교 렌더링</t>
+          <t>계약·도서 v1.0, v1.1, 최종 확정본 간의 조항 차이점 비교 렌더링</t>
         </is>
       </c>
       <c r="G13" s="249" t="inlineStr">
@@ -12823,7 +12823,7 @@
     <row r="14">
       <c r="A14" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0300</t>
+          <t>TS_QA_0300</t>
         </is>
       </c>
       <c r="B14" s="248" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="C14" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0304</t>
+          <t>TC_QA_0304</t>
         </is>
       </c>
       <c r="D14" s="248" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="E14" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="F14" s="248" t="inlineStr">
         <is>
-          <t>고위험 문구 0건인 안전 시안에 대한 다건 일괄 승인</t>
+          <t>고위험 조항 0건인 안전 계약·도서에 대한 다건 일괄 승인</t>
         </is>
       </c>
       <c r="G14" s="249" t="inlineStr">
@@ -12888,7 +12888,7 @@
     <row r="15">
       <c r="A15" s="247" t="inlineStr">
         <is>
-          <t>TS_RA_0300</t>
+          <t>TS_QA_0300</t>
         </is>
       </c>
       <c r="B15" s="248" t="inlineStr">
@@ -12898,17 +12898,17 @@
       </c>
       <c r="C15" s="247" t="inlineStr">
         <is>
-          <t>TC_RA_0305</t>
+          <t>TC_QA_0305</t>
         </is>
       </c>
       <c r="D15" s="248" t="inlineStr">
         <is>
-          <t>심의 처리 기한 초과 알림</t>
+          <t>검증 처리 기한 초과 알림</t>
         </is>
       </c>
       <c r="E15" s="247" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="F15" s="248" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="D6" s="248" t="inlineStr">
         <is>
-          <t>MarketingHub 광고심의 회신 API</t>
+          <t>SRM-Portal 계약·규격검증 회신 API</t>
         </is>
       </c>
       <c r="E6" s="247" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="F6" s="248" t="inlineStr">
         <is>
-          <t>심의 확정 데이터 및 PDF 다운로드 URL MarketingHub 정상 수신</t>
+          <t>검증 확정 데이터 및 PDF 다운로드 URL SRM-Portal 정상 수신</t>
         </is>
       </c>
       <c r="G6" s="249" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="D7" s="248" t="inlineStr">
         <is>
-          <t>ProductLab 전성분·실증 연동 및 [Option] KT 레몬 연계</t>
+          <t>PLM-Nexus 자재BOM·시험검증 연동 및 [Option] HB-Monitor 연계</t>
         </is>
       </c>
       <c r="E7" s="247" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="F7" s="248" t="inlineStr">
         <is>
-          <t>매일 새벽 원료 배합한도 변경분 수신 및 규제DB 최신화</t>
+          <t>매일 새벽 원소재 유해물질한도 변경분 수신 및 규제DB 최신화</t>
         </is>
       </c>
       <c r="G7" s="249" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="D8" s="248" t="inlineStr">
         <is>
-          <t>ProductLab 실증자료 주기적 동기화</t>
+          <t>PLM-Nexus 시험성적서 주기적 동기화</t>
         </is>
       </c>
       <c r="E8" s="247" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="F8" s="248" t="inlineStr">
         <is>
-          <t>신규 등록된 임상시험 보고서 메타데이터 자동 색인 반영</t>
+          <t>신규 등록된 신뢰성시험 보고서 메타데이터 자동 색인 반영</t>
         </is>
       </c>
       <c r="G8" s="249" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="F12" s="248" t="inlineStr">
         <is>
-          <t>모든 심의 이벤트의 불변 로그 적재 및 블록 해시 체인 무결성 확인</t>
+          <t>모든 검증 이벤트의 불변 로그 적재 및 블록 해시 체인 무결성 확인</t>
         </is>
       </c>
       <c r="G12" s="249" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="F13" s="248" t="inlineStr">
         <is>
-          <t>마케터, RA담당자, 관리자 권한별 URL 및 API 비인가 접근 완벽 차단</t>
+          <t>구매담당자, QA담당자, 관리자 권한별 URL 및 API 비인가 접근 완벽 차단</t>
         </is>
       </c>
       <c r="G13" s="249" t="inlineStr">
